--- a/Results/Phase 2/Methanol/methanol ozone depletion results.xlsx
+++ b/Results/Phase 2/Methanol/methanol ozone depletion results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.681617641686256e-07</v>
+        <v>1.675589137790846e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>3.733137631520328e-07</v>
+        <v>3.724505027701214e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.732461339089936e-07</v>
+        <v>1.704759761862794e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>1.942900799792229e-07</v>
+        <v>1.938760085733286e-07</v>
       </c>
       <c r="F33" t="n">
-        <v>1.722527299622836e-07</v>
+        <v>1.698669997412442e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>1.674382430828956e-07</v>
+        <v>1.67113151787903e-07</v>
       </c>
       <c r="H33" t="n">
-        <v>1.723887637989705e-07</v>
+        <v>1.699208614853181e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>1.749833729369724e-07</v>
+        <v>1.714643504689761e-07</v>
       </c>
       <c r="J33" t="n">
-        <v>1.694046827360392e-07</v>
+        <v>1.682740288548068e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>1.816815978993123e-07</v>
+        <v>1.754147321934066e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>1.693576730078879e-07</v>
+        <v>1.682488390823268e-07</v>
       </c>
       <c r="M33" t="n">
-        <v>1.681182130900756e-07</v>
+        <v>1.674855914986053e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.804348819890814e-07</v>
+        <v>1.747565998770846e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>7.505465637232636e-08</v>
+        <v>7.39700706695912e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.695313340795994e-07</v>
+        <v>1.683881198232523e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.72488521534462e-07</v>
+        <v>1.700644996084444e-07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.711559970981815e-07</v>
+        <v>1.692332135356157e-07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.693046097221353e-07</v>
+        <v>1.682403190012458e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>1.739024883638572e-07</v>
+        <v>1.708512354915845e-07</v>
       </c>
       <c r="U33" t="n">
-        <v>4.228335137620634e-07</v>
+        <v>4.217390387195904e-07</v>
       </c>
       <c r="V33" t="n">
-        <v>1.687878689179291e-07</v>
+        <v>1.679368303430175e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>2.927442726149327e-07</v>
+        <v>2.892170097103407e-07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.691372662309818e-07</v>
+        <v>1.680918171445896e-07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.698496178984468e-07</v>
+        <v>1.685339901129746e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.4594790362314e-07</v>
+        <v>1.452096152393556e-07</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.690039748842619e-07</v>
+        <v>1.68029874469442e-07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.677237790669286e-07</v>
+        <v>1.672492531338793e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.657696837794734e-07</v>
+        <v>1.656569396929363e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>3.711597407113108e-07</v>
+        <v>3.706566498257934e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.667231280014191e-07</v>
+        <v>1.662187861554394e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>1.929106365248873e-07</v>
+        <v>1.927120484092691e-07</v>
       </c>
       <c r="F33" t="n">
-        <v>1.659190170334386e-07</v>
+        <v>1.657380134152457e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>1.666300943642311e-07</v>
+        <v>1.661910169639371e-07</v>
       </c>
       <c r="H33" t="n">
-        <v>1.678576380330505e-07</v>
+        <v>1.668545677393015e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>1.662395537268532e-07</v>
+        <v>1.659257020216873e-07</v>
       </c>
       <c r="J33" t="n">
-        <v>1.669291287489657e-07</v>
+        <v>1.663576872007201e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>1.667747923088215e-07</v>
+        <v>1.662666724603205e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>1.663941766756731e-07</v>
+        <v>1.660375952260966e-07</v>
       </c>
       <c r="M33" t="n">
-        <v>1.66356480156805e-07</v>
+        <v>1.659958669648331e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.673921446473131e-07</v>
+        <v>1.666076794249763e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>6.899209811959303e-08</v>
+        <v>6.881704590968873e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.66857565605432e-07</v>
+        <v>1.663324043932135e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.661883267014214e-07</v>
+        <v>1.659059494169865e-07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.663274574834674e-07</v>
+        <v>1.659730641906149e-07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.668292198706009e-07</v>
+        <v>1.663129080576452e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>1.663110592612439e-07</v>
+        <v>1.659674394737702e-07</v>
       </c>
       <c r="U33" t="n">
-        <v>4.177862303787002e-07</v>
+        <v>4.172753162774052e-07</v>
       </c>
       <c r="V33" t="n">
-        <v>1.673621592630481e-07</v>
+        <v>1.66643726838565e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>2.87652522280159e-07</v>
+        <v>2.846170109066741e-07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.675858644309799e-07</v>
+        <v>1.667422920927794e-07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.666077486447985e-07</v>
+        <v>1.661491054108804e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.427942351265192e-07</v>
+        <v>1.422393756112994e-07</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.688085206379626e-07</v>
+        <v>1.674526322145686e-07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.658223807442577e-07</v>
+        <v>1.656784475532526e-07</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.671198166811375e-07</v>
+        <v>1.667995747570443e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>3.725332354248716e-07</v>
+        <v>3.718576799106233e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.686272527698798e-07</v>
+        <v>1.676554950141733e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>1.944685192638865e-07</v>
+        <v>1.938833829361674e-07</v>
       </c>
       <c r="F33" t="n">
-        <v>1.693727533325434e-07</v>
+        <v>1.680867388012664e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>1.668950609046791e-07</v>
+        <v>1.666598237043873e-07</v>
       </c>
       <c r="H33" t="n">
-        <v>1.701325074154568e-07</v>
+        <v>1.684976034043724e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>1.712301159835366e-07</v>
+        <v>1.6915706786576e-07</v>
       </c>
       <c r="J33" t="n">
-        <v>1.684105065290482e-07</v>
+        <v>1.675563363436349e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>1.780758825729495e-07</v>
+        <v>1.733632175131195e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>1.672612305464509e-07</v>
+        <v>1.668729622938032e-07</v>
       </c>
       <c r="M33" t="n">
-        <v>1.672821088371191e-07</v>
+        <v>1.668689852519371e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.749958730664355e-07</v>
+        <v>1.714233865168382e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>7.283863404394492e-08</v>
+        <v>7.219052932123308e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.682485392169685e-07</v>
+        <v>1.674854424200484e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.702465267796838e-07</v>
+        <v>1.686223755888594e-07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.696768288164258e-07</v>
+        <v>1.682469109010756e-07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.682438101536291e-07</v>
+        <v>1.674777272702623e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>1.68978599508553e-07</v>
+        <v>1.678603793390673e-07</v>
       </c>
       <c r="U33" t="n">
-        <v>4.208855643751495e-07</v>
+        <v>4.203063104285273e-07</v>
       </c>
       <c r="V33" t="n">
-        <v>1.679359981992642e-07</v>
+        <v>1.673042044805838e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>2.952599863964988e-07</v>
+        <v>2.904574991034135e-07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.688851073448303e-07</v>
+        <v>1.678158431013774e-07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.697785901140662e-07</v>
+        <v>1.683712032229831e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.450955083397524e-07</v>
+        <v>1.444802994438426e-07</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.681071326948323e-07</v>
+        <v>1.673727175445917e-07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.672971495966859e-07</v>
+        <v>1.668699772515652e-07</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.662996290088597e-07</v>
+        <v>1.661309245144553e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>3.742213999462782e-07</v>
+        <v>3.727109910317768e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.686293727454049e-07</v>
+        <v>1.674827769117973e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>1.951447831273652e-07</v>
+        <v>1.94172878573689e-07</v>
       </c>
       <c r="F33" t="n">
-        <v>1.669833644498771e-07</v>
+        <v>1.665200861215765e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>1.664710277108767e-07</v>
+        <v>1.662345673798368e-07</v>
       </c>
       <c r="H33" t="n">
-        <v>1.68650913476445e-07</v>
+        <v>1.674614312336095e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>1.672803985137134e-07</v>
+        <v>1.666894532233591e-07</v>
       </c>
       <c r="J33" t="n">
-        <v>1.675667365629101e-07</v>
+        <v>1.668826692635821e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>1.666377344671639e-07</v>
+        <v>1.663275778550683e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>1.661426419563429e-07</v>
+        <v>1.660332849952864e-07</v>
       </c>
       <c r="M33" t="n">
-        <v>1.668429266445728e-07</v>
+        <v>1.664341964877513e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.708143161747481e-07</v>
+        <v>1.687816827141217e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>7.062103078505819e-08</v>
+        <v>7.02849318645892e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.674970110588057e-07</v>
+        <v>1.668638234398095e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.679596560338965e-07</v>
+        <v>1.671092221406168e-07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.679503725835589e-07</v>
+        <v>1.67070317919074e-07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.674660251716801e-07</v>
+        <v>1.668400042191242e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>1.669466145021112e-07</v>
+        <v>1.664975343382398e-07</v>
       </c>
       <c r="U33" t="n">
-        <v>4.196460488847116e-07</v>
+        <v>4.18969178337646e-07</v>
       </c>
       <c r="V33" t="n">
-        <v>1.673869959806954e-07</v>
+        <v>1.668054687076322e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>2.92683239974961e-07</v>
+        <v>2.882669735171021e-07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.679082543104938e-07</v>
+        <v>1.670676724604203e-07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.676904272517269e-07</v>
+        <v>1.669527740424902e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.438651879799528e-07</v>
+        <v>1.433270008596501e-07</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.672441611594708e-07</v>
+        <v>1.666856513605995e-07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.667089422313616e-07</v>
+        <v>1.663496905519978e-07</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.661776692403016e-07</v>
+        <v>1.65959941462843e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>3.742840294485504e-07</v>
+        <v>3.726383764589617e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.665459780305976e-07</v>
+        <v>1.661655411988784e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>1.940054492157218e-07</v>
+        <v>1.93431881325792e-07</v>
       </c>
       <c r="F33" t="n">
-        <v>1.670280727470808e-07</v>
+        <v>1.664443212597092e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>1.663624167021776e-07</v>
+        <v>1.660728556631206e-07</v>
       </c>
       <c r="H33" t="n">
-        <v>1.681893236703098e-07</v>
+        <v>1.670879513984269e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>1.664052710192766e-07</v>
+        <v>1.660774100043637e-07</v>
       </c>
       <c r="J33" t="n">
-        <v>1.67210373199098e-07</v>
+        <v>1.665714385922093e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>1.661691189815782e-07</v>
+        <v>1.65944176970782e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>1.662941891167718e-07</v>
+        <v>1.660242474866924e-07</v>
       </c>
       <c r="M33" t="n">
-        <v>1.665778583594375e-07</v>
+        <v>1.661799790499067e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.692983347310911e-07</v>
+        <v>1.677832498081426e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>6.957407703182039e-08</v>
+        <v>6.933089355046155e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.671571032242262e-07</v>
+        <v>1.665675265846841e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.675168514693564e-07</v>
+        <v>1.66753908724542e-07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.675056731168302e-07</v>
+        <v>1.667073062188081e-07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.671287931693645e-07</v>
+        <v>1.665401862045784e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>1.667430070741023e-07</v>
+        <v>1.662735512380302e-07</v>
       </c>
       <c r="U33" t="n">
-        <v>4.19388399818287e-07</v>
+        <v>4.184480003647518e-07</v>
       </c>
       <c r="V33" t="n">
-        <v>1.673010208767054e-07</v>
+        <v>1.666604039701613e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>2.90729093172772e-07</v>
+        <v>2.866717441316844e-07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.671534360715365e-07</v>
+        <v>1.665292323025847e-07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.669027171774371e-07</v>
+        <v>1.663781203881354e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.425894521662488e-07</v>
+        <v>1.422069703740067e-07</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.673005299004345e-07</v>
+        <v>1.666149453347211e-07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.66327670815527e-07</v>
+        <v>1.660254341848282e-07</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.668351166622073e-07</v>
+        <v>1.664645232403564e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>3.707009918228403e-07</v>
+        <v>3.705549380929144e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.700722594335032e-07</v>
+        <v>1.683353829812947e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>1.942758770002127e-07</v>
+        <v>1.936557522906007e-07</v>
       </c>
       <c r="F33" t="n">
-        <v>1.669374360555977e-07</v>
+        <v>1.664980740139769e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>1.665747025096083e-07</v>
+        <v>1.663041149794948e-07</v>
       </c>
       <c r="H33" t="n">
-        <v>1.689212916104962e-07</v>
+        <v>1.676265692064721e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>1.683580110936894e-07</v>
+        <v>1.673227489263608e-07</v>
       </c>
       <c r="J33" t="n">
-        <v>1.676723116302844e-07</v>
+        <v>1.669593447256817e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>1.716762063746364e-07</v>
+        <v>1.693957845186747e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>1.683286022511719e-07</v>
+        <v>1.673953562145521e-07</v>
       </c>
       <c r="M33" t="n">
-        <v>1.667342831464277e-07</v>
+        <v>1.663832391380916e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.712412634170891e-07</v>
+        <v>1.690771481389117e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>7.102629817732525e-08</v>
+        <v>7.055915354994128e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.674482609586763e-07</v>
+        <v>1.668370810587301e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.683666882997326e-07</v>
+        <v>1.673686334141451e-07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.677573901223221e-07</v>
+        <v>1.669631548699612e-07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.684613878191188e-07</v>
+        <v>1.675164951940507e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>1.67621035662709e-07</v>
+        <v>1.669102397885027e-07</v>
       </c>
       <c r="U33" t="n">
-        <v>4.214670916900972e-07</v>
+        <v>4.200835460328597e-07</v>
       </c>
       <c r="V33" t="n">
-        <v>1.669018046924544e-07</v>
+        <v>1.665051884035667e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>2.922829962385801e-07</v>
+        <v>2.880243236092622e-07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.693102854217739e-07</v>
+        <v>1.678995685595056e-07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.678155002764488e-07</v>
+        <v>1.670327364717897e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.437399733219997e-07</v>
+        <v>1.431789313392893e-07</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.679378478218509e-07</v>
+        <v>1.671023959962327e-07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.669896107464731e-07</v>
+        <v>1.665220806882147e-07</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.657756229785624e-07</v>
+        <v>1.656366195305561e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>3.704991003000432e-07</v>
+        <v>3.70226466949753e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.668564785496747e-07</v>
+        <v>1.66276746152873e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>1.929776620712688e-07</v>
+        <v>1.927358147571691e-07</v>
       </c>
       <c r="F33" t="n">
-        <v>1.658936689513743e-07</v>
+        <v>1.656978768848154e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>1.667950500787421e-07</v>
+        <v>1.662820975095255e-07</v>
       </c>
       <c r="H33" t="n">
-        <v>1.682656962026217e-07</v>
+        <v>1.670634630657002e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>1.664301164734095e-07</v>
+        <v>1.66012968348777e-07</v>
       </c>
       <c r="J33" t="n">
-        <v>1.668304334681719e-07</v>
+        <v>1.662838144739185e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>1.664915761068547e-07</v>
+        <v>1.660664951695164e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>1.661047201828638e-07</v>
+        <v>1.658407684880545e-07</v>
       </c>
       <c r="M33" t="n">
-        <v>1.662375551479819e-07</v>
+        <v>1.659090900366954e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.671366685249517e-07</v>
+        <v>1.66450941042023e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>6.91047224178678e-08</v>
+        <v>6.885869228358219e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.663560108584313e-07</v>
+        <v>1.659939946581246e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.661535764713846e-07</v>
+        <v>1.658671780300644e-07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.664325626749471e-07</v>
+        <v>1.660099934477982e-07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.672380851434449e-07</v>
+        <v>1.665665194933146e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>1.661439439515774e-07</v>
+        <v>1.658481025079871e-07</v>
       </c>
       <c r="U33" t="n">
-        <v>4.1683588899703e-07</v>
+        <v>4.166171243272869e-07</v>
       </c>
       <c r="V33" t="n">
-        <v>1.66789904334457e-07</v>
+        <v>1.662686007742222e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>2.869163440059824e-07</v>
+        <v>2.841884494546424e-07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.676150944009193e-07</v>
+        <v>1.667391801163912e-07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.66267122939109e-07</v>
+        <v>1.659236608294185e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.421518226536761e-07</v>
+        <v>1.417374587763248e-07</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.684366394157429e-07</v>
+        <v>1.672135435053948e-07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.656793886416764e-07</v>
+        <v>1.655689276220051e-07</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.656144041072594e-07</v>
+        <v>1.654650427133501e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>3.700867912107811e-07</v>
+        <v>3.698830620795626e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.665634276786843e-07</v>
+        <v>1.660212356513151e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>1.927307028466231e-07</v>
+        <v>1.925313327496668e-07</v>
       </c>
       <c r="F33" t="n">
-        <v>1.657635455553877e-07</v>
+        <v>1.655427406998406e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>1.662685640392374e-07</v>
+        <v>1.658718494929108e-07</v>
       </c>
       <c r="H33" t="n">
-        <v>1.677430345066889e-07</v>
+        <v>1.666867673499306e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>1.661333600063297e-07</v>
+        <v>1.657595262739265e-07</v>
       </c>
       <c r="J33" t="n">
-        <v>1.664729131580757e-07</v>
+        <v>1.659832933897416e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>1.660412310559547e-07</v>
+        <v>1.657141969115082e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>1.658416591562269e-07</v>
+        <v>1.65603043899235e-07</v>
       </c>
       <c r="M33" t="n">
-        <v>1.662196121151089e-07</v>
+        <v>1.658160898316099e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.667844493891856e-07</v>
+        <v>1.66157077391687e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>6.850276816454547e-08</v>
+        <v>6.829229562839916e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.658575438076276e-07</v>
+        <v>1.65616468181169e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.658062521116331e-07</v>
+        <v>1.655764967104044e-07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.659684154774852e-07</v>
+        <v>1.656598223697217e-07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.666540356035413e-07</v>
+        <v>1.661106995336231e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>1.660908881443228e-07</v>
+        <v>1.657378106343224e-07</v>
       </c>
       <c r="U33" t="n">
-        <v>4.165822642043633e-07</v>
+        <v>4.162184226394231e-07</v>
       </c>
       <c r="V33" t="n">
-        <v>1.670760969748372e-07</v>
+        <v>1.663696729551207e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>2.849146665224639e-07</v>
+        <v>2.826606733857595e-07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.674529957107863e-07</v>
+        <v>1.665736747773718e-07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.658515055743537e-07</v>
+        <v>1.655997257991294e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.414237174776512e-07</v>
+        <v>1.411216676853336e-07</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.681668137276828e-07</v>
+        <v>1.669743534140713e-07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.657084662798789e-07</v>
+        <v>1.655075332800864e-07</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.673783812607029e-07</v>
+        <v>1.668984816033244e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>3.713012528840326e-07</v>
+        <v>3.710400829789987e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.700972486415542e-07</v>
+        <v>1.684449921099013e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>1.93856574266731e-07</v>
+        <v>1.934703276892951e-07</v>
       </c>
       <c r="F33" t="n">
-        <v>1.682708503138812e-07</v>
+        <v>1.673848133478931e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>1.666837305985445e-07</v>
+        <v>1.66469170322691e-07</v>
       </c>
       <c r="H33" t="n">
-        <v>1.69778537039681e-07</v>
+        <v>1.682283854634438e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>1.713633528045077e-07</v>
+        <v>1.691813595718617e-07</v>
       </c>
       <c r="J33" t="n">
-        <v>1.681339924199403e-07</v>
+        <v>1.673325275738891e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>1.747106698114939e-07</v>
+        <v>1.71351011836101e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>1.670767019314599e-07</v>
+        <v>1.667025573133054e-07</v>
       </c>
       <c r="M33" t="n">
-        <v>1.671467865989185e-07</v>
+        <v>1.667331895441851e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.757086267069911e-07</v>
+        <v>1.717805687229425e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>7.241099625864406e-08</v>
+        <v>7.175795422135016e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.680916861058916e-07</v>
+        <v>1.673285091625355e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.695042646522518e-07</v>
+        <v>1.681384121281692e-07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.689356816439267e-07</v>
+        <v>1.677528030867454e-07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.685764712903551e-07</v>
+        <v>1.676492415240257e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>1.696385314153602e-07</v>
+        <v>1.681794944071985e-07</v>
       </c>
       <c r="U33" t="n">
-        <v>4.204522918574278e-07</v>
+        <v>4.197708524337079e-07</v>
       </c>
       <c r="V33" t="n">
-        <v>1.678185331480849e-07</v>
+        <v>1.671725270378452e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>2.91580480022982e-07</v>
+        <v>2.879444909741641e-07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.692471497974514e-07</v>
+        <v>1.679633978857415e-07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.686998065560804e-07</v>
+        <v>1.676659289733414e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.446833202155477e-07</v>
+        <v>1.440710536346851e-07</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.680305034746657e-07</v>
+        <v>1.672634366870315e-07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.670640580231315e-07</v>
+        <v>1.66669522221782e-07</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.661059462005077e-07</v>
+        <v>1.659381253037133e-07</v>
       </c>
       <c r="C33" t="n">
-        <v>3.71026578156441e-07</v>
+        <v>3.706662215983631e-07</v>
       </c>
       <c r="D33" t="n">
-        <v>1.671141954751172e-07</v>
+        <v>1.665236770321882e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>1.936818467647024e-07</v>
+        <v>1.932328419918112e-07</v>
       </c>
       <c r="F33" t="n">
-        <v>1.660320376395269e-07</v>
+        <v>1.658838999661678e-07</v>
       </c>
       <c r="G33" t="n">
-        <v>1.668575123374508e-07</v>
+        <v>1.66407553665155e-07</v>
       </c>
       <c r="H33" t="n">
-        <v>1.687119584102133e-07</v>
+        <v>1.67414674380645e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>1.666186963870779e-07</v>
+        <v>1.662255717708461e-07</v>
       </c>
       <c r="J33" t="n">
-        <v>1.672067381846131e-07</v>
+        <v>1.666009717814226e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>1.674553558434121e-07</v>
+        <v>1.667591939610505e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>1.664348136928514e-07</v>
+        <v>1.661362467588899e-07</v>
       </c>
       <c r="M33" t="n">
-        <v>1.664542968087755e-07</v>
+        <v>1.66135574318878e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.682799146619584e-07</v>
+        <v>1.672112800904035e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>6.957881112547698e-08</v>
+        <v>6.939463693041897e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.676103436380653e-07</v>
+        <v>1.668637606183715e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.672975846281644e-07</v>
+        <v>1.666620969318665e-07</v>
       </c>
       <c r="R33" t="n">
-        <v>1.669059535592413e-07</v>
+        <v>1.66388125552591e-07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.675562714904133e-07</v>
+        <v>1.668435713528511e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>1.664451778320192e-07</v>
+        <v>1.66126690892608e-07</v>
       </c>
       <c r="U33" t="n">
-        <v>4.179051531559784e-07</v>
+        <v>4.176362434411624e-07</v>
       </c>
       <c r="V33" t="n">
-        <v>1.671974616283468e-07</v>
+        <v>1.666166639995771e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>2.897003002249409e-07</v>
+        <v>2.861691551048838e-07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.681929695224276e-07</v>
+        <v>1.671707343650941e-07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.669880737049257e-07</v>
+        <v>1.664577599332901e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.430189213145535e-07</v>
+        <v>1.42583183206043e-07</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.672267286099331e-07</v>
+        <v>1.665975710081594e-07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.672680008539644e-07</v>
+        <v>1.66595992374483e-07</v>
       </c>
     </row>
   </sheetData>
